--- a/CDA_TESTING_JIRA.xlsx
+++ b/CDA_TESTING_JIRA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arora/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC103C5-1D7B-4541-84F6-880E0207B55D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5F43AD-D552-F743-8FBF-E6B5F3E76DE0}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" activeTab="1" xr2:uid="{82B421E3-375F-3740-A65A-2FECAD24F0CC}"/>
+    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16460" xr2:uid="{82B421E3-375F-3740-A65A-2FECAD24F0CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>Title</t>
   </si>
@@ -390,261 +390,6 @@
   </si>
   <si>
     <t>Document results, defects, and resolutions. Obtain formal sign-off for CDA migration.</t>
-  </si>
-  <si>
-    <t>Task Segment</t>
-  </si>
-  <si>
-    <t>Refresher &amp; Alignment</t>
-  </si>
-  <si>
-    <t>CDA Process Understanding &amp; Knowledge Refresh</t>
-  </si>
-  <si>
-    <t>Conduct a detailed walkthrough of the CDA (Cloud Data Access) architecture including Guidewire export → S3 → Databricks ingestion → Clone → SCD → ODS Views. Ensure QA team understands differences between Read Replica and CDA pipelines, especially CDC handling and SCD logic.</t>
-  </si>
-  <si>
-    <t>Review Existing Test Strategy &amp; Plan</t>
-  </si>
-  <si>
-    <t>Revisit previously created test strategy and test plan. Update it to include CDA-specific validation such as CDC logic, watermark alignment, and SCD validation. Identify gaps and update documentation accordingly.</t>
-  </si>
-  <si>
-    <t>Review Partial Automation Framework</t>
-  </si>
-  <si>
-    <t>Analyze existing automation scripts developed during PoC phase. Identify reusable components, limitations, and required enhancements to scale for ~2000 tables.</t>
-  </si>
-  <si>
-    <t>Environment Setup</t>
-  </si>
-  <si>
-    <t>Validate Test &amp; Build Environments</t>
-  </si>
-  <si>
-    <t>Ensure Databricks environments (Build/Test) are configured with access to both Read Replica processed data (ADF) and CDA processed data (S3 ingestion). Validate catalog/schema access and permissions.</t>
-  </si>
-  <si>
-    <t>Data Availability Verification</t>
-  </si>
-  <si>
-    <t>Confirm that both pipelines (Read Replica and CDA) are actively populating data in parallel for selected entities. Validate data completeness before starting comparisons.</t>
-  </si>
-  <si>
-    <t>Watermark / Data Cutoff Alignment</t>
-  </si>
-  <si>
-    <t>Identify mechanism to determine common comparison point (T_ASOF). Validate CDC ingestion completeness using watermark tables or max commit timestamp.</t>
-  </si>
-  <si>
-    <t>Data Profiling &amp; Preparation</t>
-  </si>
-  <si>
-    <t>Identify High Volume Tables</t>
-  </si>
-  <si>
-    <t>Profile all tables and categorize based on volume (row count, size). Prioritize critical/high-volume tables for early validation.</t>
-  </si>
-  <si>
-    <t>Identify Tables with Large Columns (~1MB Data)</t>
-  </si>
-  <si>
-    <t>Scan metadata and actual data to identify tables/columns that store large payloads (e.g., documents, JSON blobs, notes fields up to ~1MB). Ensure these are flagged for special validation.</t>
-  </si>
-  <si>
-    <t>Validate Large Column Data Handling</t>
-  </si>
-  <si>
-    <t>Perform targeted testing on identified large columns to ensure no truncation, encoding issues, or performance degradation occurs during CDA ingestion and processing.</t>
-  </si>
-  <si>
-    <t>Define Table Mapping (RR vs CDA)</t>
-  </si>
-  <si>
-    <t>Create and validate mapping between Read Replica tables and corresponding CDA Clone/SCD/ODS tables. Ensure 1:1 comparison alignment.</t>
-  </si>
-  <si>
-    <t>Build / Setup Validation</t>
-  </si>
-  <si>
-    <t>Validate Clone Table Ingestion</t>
-  </si>
-  <si>
-    <t>Verify that CDA Clone tables correctly ingest raw CDC data from S3 including inserts, updates, and deletes. Validate structure and metadata fields.</t>
-  </si>
-  <si>
-    <t>Validate SCD Processing Logic</t>
-  </si>
-  <si>
-    <t>Validate SCD (Type 2) logic including start_at, end_at, and current record identification. Ensure no overlapping records and correct history tracking.</t>
-  </si>
-  <si>
-    <t>Validate ODS View Logic (CDA)</t>
-  </si>
-  <si>
-    <t>Validate that CDA-based ODS Views correctly replicate functionality of existing Read Replica ODS Views. This is critical for downstream Silver/Gold compatibility.</t>
-  </si>
-  <si>
-    <t>Schema Comparison Validation</t>
-  </si>
-  <si>
-    <t>Compare schema (DDL) between Read Replica ODS tables and CDA ODS Views including column names, data types, nullability, and structure consistency.</t>
-  </si>
-  <si>
-    <t>Automation Framework</t>
-  </si>
-  <si>
-    <t>Design Scalable Comparison Framework</t>
-  </si>
-  <si>
-    <t>Enhance automation framework to support large-scale table comparison (2000+ tables) using configuration-driven approach.</t>
-  </si>
-  <si>
-    <t>Implement Row-to-Row Comparison Logic</t>
-  </si>
-  <si>
-    <t>Develop generic comparison logic using full-row hash comparison for efficient validation without column-level dependency.</t>
-  </si>
-  <si>
-    <t>Implement Count &amp; Schema Validation</t>
-  </si>
-  <si>
-    <t>Automate validation of row counts, schema consistency, and partition-level data checks.</t>
-  </si>
-  <si>
-    <t>Implement CDC / SCD Validation Automation</t>
-  </si>
-  <si>
-    <t>Automate checks for SCD correctness (single current record, no overlaps) and CDC completeness.</t>
-  </si>
-  <si>
-    <t>Integrate Large Column Validation in Automation</t>
-  </si>
-  <si>
-    <t>Extend automation to handle and validate large column data (~1MB) ensuring no truncation or mismatch.</t>
-  </si>
-  <si>
-    <t>Orchestration &amp; Scheduling</t>
-  </si>
-  <si>
-    <t>Design Test Execution Workflow</t>
-  </si>
-  <si>
-    <t>Define orchestration workflow using Databricks Jobs or Workflows to execute tests in parallel batches.</t>
-  </si>
-  <si>
-    <t>Implement Scheduling Strategy</t>
-  </si>
-  <si>
-    <t>Configure automated test execution on daily basis (post data load) and optional intra-day runs for critical tables.</t>
-  </si>
-  <si>
-    <t>Configure Failure Alerts &amp; Notifications</t>
-  </si>
-  <si>
-    <t>Integrate alerting mechanism (email/Slack/Teams) for test failures and anomalies detected during execution.</t>
-  </si>
-  <si>
-    <t>Testing Execution</t>
-  </si>
-  <si>
-    <t>PoC Execution for Selected Tables</t>
-  </si>
-  <si>
-    <t>Execute initial validation on a subset of critical tables to validate approach and fine-tune logic.</t>
-  </si>
-  <si>
-    <t>Full Scale Automation Execution</t>
-  </si>
-  <si>
-    <t>Run automated comparison across all mapped tables between Read Replica and CDA pipelines.</t>
-  </si>
-  <si>
-    <t>Manual Testing for Critical Scenarios</t>
-  </si>
-  <si>
-    <t>Perform manual validation for complex scenarios such as CDC edge cases, deletes, and large column handling.</t>
-  </si>
-  <si>
-    <t>Defect Identification &amp; Logging</t>
-  </si>
-  <si>
-    <t>Log discrepancies identified during comparison including missing records, mismatches, schema issues, or CDC inconsistencies.</t>
-  </si>
-  <si>
-    <t>Defect Analysis &amp; Resolution Support</t>
-  </si>
-  <si>
-    <t>Work with engineering teams to analyze root causes and validate fixes for identified defects.</t>
-  </si>
-  <si>
-    <t>Parallel Run Monitoring</t>
-  </si>
-  <si>
-    <t>Continuous Data Monitoring</t>
-  </si>
-  <si>
-    <t>Monitor both pipelines during parallel run period to detect anomalies over time.</t>
-  </si>
-  <si>
-    <t>Trend Analysis &amp; Stability Validation</t>
-  </si>
-  <si>
-    <t>Analyze test results over multiple days to ensure stability and consistency of CDA pipeline.</t>
-  </si>
-  <si>
-    <t>Regression Validation</t>
-  </si>
-  <si>
-    <t>Re-run tests after fixes or changes to ensure no regression issues are introduced.</t>
-  </si>
-  <si>
-    <t>Pre-Go Live Validation</t>
-  </si>
-  <si>
-    <t>ODS View Final Validation</t>
-  </si>
-  <si>
-    <t>Perform final validation of CDA ODS Views to ensure full compatibility with downstream Silver/Gold pipelines.</t>
-  </si>
-  <si>
-    <t>Switch-over Simulation Testing</t>
-  </si>
-  <si>
-    <t>Simulate switch from Read Replica ODS to CDA ODS Views and validate downstream processing.</t>
-  </si>
-  <si>
-    <t>Performance Validation</t>
-  </si>
-  <si>
-    <t>Validate performance of CDA ingestion and Databricks processing including large data handling.</t>
-  </si>
-  <si>
-    <t>Sign-off Readiness Assessment</t>
-  </si>
-  <si>
-    <t>Prepare final validation report summarizing comparison results, defect status, and readiness for go-live.</t>
-  </si>
-  <si>
-    <t>Go Live Support</t>
-  </si>
-  <si>
-    <t>Post Go-Live Monitoring</t>
-  </si>
-  <si>
-    <t>Monitor data consistency after switching to CDA pipeline in production.</t>
-  </si>
-  <si>
-    <t>Switch-over Validation Testing</t>
-  </si>
-  <si>
-    <t>Validate that all downstream systems are functioning correctly after switching to CDA.</t>
-  </si>
-  <si>
-    <t>Legacy Decommission Validation</t>
-  </si>
-  <si>
-    <t>Validate that legacy Read Replica-based pipeline can be safely retired after successful CDA migration.</t>
   </si>
 </sst>
 </file>
@@ -1293,345 +1038,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8935FFD7-D1EB-9A48-8D07-C6FCD82149E2}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" t="s">
-        <v>91</v>
-      </c>
+      <c r="A8" s="1"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
+      <c r="A12" s="1"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B25" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B29" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B31" t="s">
-        <v>135</v>
-      </c>
-      <c r="C31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>140</v>
-      </c>
-      <c r="C33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>149</v>
-      </c>
-      <c r="C37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>151</v>
-      </c>
-      <c r="C38" t="s">
-        <v>152</v>
-      </c>
+      <c r="A16" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
